--- a/jpcore-r4/feature/swg45-JP_Condition_Diagnosis関係の指摘対応①/StructureDefinition-jp-immunization-duedateofnextdose.xlsx
+++ b/jpcore-r4/feature/swg45-JP_Condition_Diagnosis関係の指摘対応①/StructureDefinition-jp-immunization-duedateofnextdose.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-09T02:16:31+00:00</t>
+    <t>2024-11-09T04:34:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
